--- a/output/StructureDefinition-Consent.xlsx
+++ b/output/StructureDefinition-Consent.xlsx
@@ -4594,7 +4594,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>78</v>
